--- a/data/social_data.xlsx
+++ b/data/social_data.xlsx
@@ -9274,7 +9274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M306"/>
+  <dimension ref="A1:N306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9357,6 +9357,11 @@
           <t>context</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>yomi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -9528,6 +9533,11 @@
       </c>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ローマきょうこう[ほうおう]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -9585,6 +9595,11 @@
       </c>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="5" t="n"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>じゅうじぐん</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -9642,6 +9657,11 @@
       </c>
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ルネサンス[ぶんげいふっこう]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -9699,6 +9719,11 @@
       </c>
       <c r="L7" s="5" t="n"/>
       <c r="M7" s="5" t="n"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>しゅうきょうかいかく</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -9756,6 +9781,11 @@
       </c>
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="3" t="n"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>いえずすかい</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -9813,6 +9843,11 @@
       </c>
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="5" t="n"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>こうしんりょう</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -9870,6 +9905,11 @@
       </c>
       <c r="L10" s="3" t="n"/>
       <c r="M10" s="3" t="n"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>だいこうかいじだい</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -10098,6 +10138,11 @@
       </c>
       <c r="L14" s="3" t="n"/>
       <c r="M14" s="3" t="n"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>いんかていこく</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -10212,6 +10257,11 @@
       </c>
       <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>てっぽう</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -10269,6 +10319,11 @@
       </c>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="5" t="n"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>なんばんぼうえき</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -10668,6 +10723,11 @@
       </c>
       <c r="L24" s="3" t="n"/>
       <c r="M24" s="3" t="n"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>たねがしま</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -10786,6 +10846,11 @@
       </c>
       <c r="L26" s="3" t="n"/>
       <c r="M26" s="3" t="n"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>ぎん</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -11364,6 +11429,11 @@
       </c>
       <c r="L36" s="3" t="n"/>
       <c r="M36" s="3" t="n"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>おだのぶなが</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -11421,6 +11491,11 @@
       </c>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="5" t="n"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>むろまち</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -11478,6 +11553,11 @@
       </c>
       <c r="L38" s="3" t="n"/>
       <c r="M38" s="3" t="n"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>ながしののたたかい</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -11535,6 +11615,11 @@
       </c>
       <c r="L39" s="5" t="n"/>
       <c r="M39" s="5" t="n"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>あづちじょう</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -11592,6 +11677,11 @@
       </c>
       <c r="L40" s="3" t="n"/>
       <c r="M40" s="3" t="n"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>らくいち・らくざ</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -11649,6 +11739,11 @@
       </c>
       <c r="L41" s="5" t="n"/>
       <c r="M41" s="5" t="n"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>とよとみひでよし</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -11706,6 +11801,11 @@
       </c>
       <c r="L42" s="3" t="n"/>
       <c r="M42" s="3" t="n"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>かたながり</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -11763,6 +11863,11 @@
       </c>
       <c r="L43" s="5" t="n"/>
       <c r="M43" s="5" t="n"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>たいこうけんち</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -11820,6 +11925,11 @@
       </c>
       <c r="L44" s="3" t="n"/>
       <c r="M44" s="3" t="n"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>へいのうぶんり</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -11877,6 +11987,11 @@
       </c>
       <c r="L45" s="5" t="n"/>
       <c r="M45" s="5" t="n"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>きりすときょう</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -11934,6 +12049,11 @@
       </c>
       <c r="L46" s="3" t="n"/>
       <c r="M46" s="3" t="n"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>ちょうせん</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -11991,6 +12111,11 @@
       </c>
       <c r="L47" s="5" t="n"/>
       <c r="M47" s="5" t="n"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>てんしゅ</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -12048,6 +12173,11 @@
       </c>
       <c r="L48" s="3" t="n"/>
       <c r="M48" s="3" t="n"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>せんのりきゅう</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -12105,6 +12235,11 @@
       </c>
       <c r="L49" s="5" t="n"/>
       <c r="M49" s="5" t="n"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>ももやまぶんか</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -12162,6 +12297,11 @@
       </c>
       <c r="L50" s="3" t="n"/>
       <c r="M50" s="3" t="n"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>なんばんぶんか</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -12219,6 +12359,11 @@
       </c>
       <c r="L51" s="5" t="n"/>
       <c r="M51" s="5" t="n"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>かぶきおどり</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -12276,6 +12421,11 @@
       </c>
       <c r="L52" s="3" t="n"/>
       <c r="M52" s="3" t="n"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>ながしののたたかい</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -12455,6 +12605,11 @@
       </c>
       <c r="L55" s="5" t="n"/>
       <c r="M55" s="5" t="n"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>いち</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -12512,6 +12667,11 @@
       </c>
       <c r="L56" s="3" t="n"/>
       <c r="M56" s="3" t="n"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>ざ</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -12630,6 +12790,11 @@
       </c>
       <c r="L58" s="3" t="n"/>
       <c r="M58" s="3" t="n"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>かのうえいとく</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -12687,6 +12852,11 @@
       </c>
       <c r="L59" s="5" t="n"/>
       <c r="M59" s="5" t="n"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>ちゃのゆ</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -12744,6 +12914,11 @@
       </c>
       <c r="L60" s="3" t="n"/>
       <c r="M60" s="3" t="n"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>かぶきおどり</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -12858,6 +13033,11 @@
       </c>
       <c r="L62" s="3" t="n"/>
       <c r="M62" s="3" t="n"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>かたながりれい</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -12919,6 +13099,11 @@
         </is>
       </c>
       <c r="M63" s="5" t="n"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>いっき</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -12980,6 +13165,11 @@
         </is>
       </c>
       <c r="M64" s="3" t="n"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>ねんぐ</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -13094,6 +13284,11 @@
       </c>
       <c r="L66" s="3" t="n"/>
       <c r="M66" s="3" t="n"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>てっぽう</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -13208,6 +13403,11 @@
       </c>
       <c r="L68" s="3" t="n"/>
       <c r="M68" s="3" t="n"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>なんばんぼうえき</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -13265,6 +13465,11 @@
       </c>
       <c r="L69" s="5" t="n"/>
       <c r="M69" s="5" t="n"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>おだのぶなが</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -13322,6 +13527,11 @@
       </c>
       <c r="L70" s="3" t="n"/>
       <c r="M70" s="3" t="n"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>たいこうけんち</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -13379,6 +13589,11 @@
       </c>
       <c r="L71" s="5" t="n"/>
       <c r="M71" s="5" t="n"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>かたながり</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -13436,6 +13651,11 @@
       </c>
       <c r="L72" s="3" t="n"/>
       <c r="M72" s="3" t="n"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>とよとみひでよし</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -13493,6 +13713,11 @@
       </c>
       <c r="L73" s="5" t="n"/>
       <c r="M73" s="5" t="n"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>じゅうじぐん</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -13550,6 +13775,11 @@
       </c>
       <c r="L74" s="3" t="n"/>
       <c r="M74" s="3" t="n"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>しゅうきょうかいかく</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -13664,6 +13894,11 @@
       </c>
       <c r="L76" s="3" t="n"/>
       <c r="M76" s="3" t="n"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>へいのうぶんり</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -13725,6 +13960,11 @@
           <t>長篠の戦い</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>てっぽう</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -13786,6 +14026,11 @@
           <t>刀狩令</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>ひゃくしょう</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -13847,6 +14092,11 @@
           <t>唐獅子図屏風</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>かのうえいとく</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -13908,6 +14158,11 @@
           <t>唐獅子図屏風</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>ももやまぶんか</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -13969,6 +14224,11 @@
         </is>
       </c>
       <c r="M81" s="5" t="n"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>きいと／かやく</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -14201,6 +14461,11 @@
       </c>
       <c r="L85" s="5" t="n"/>
       <c r="M85" s="5" t="n"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>おだのぶなが</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -14319,6 +14584,11 @@
       </c>
       <c r="L87" s="5" t="n"/>
       <c r="M87" s="5" t="n"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>とよとみひでよし</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -14433,6 +14703,11 @@
       </c>
       <c r="L89" s="5" t="n"/>
       <c r="M89" s="5" t="n"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>ももやまぶんか</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -14604,6 +14879,11 @@
       </c>
       <c r="L92" s="3" t="n"/>
       <c r="M92" s="3" t="n"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>とくがわいえやす</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -14661,6 +14941,11 @@
       </c>
       <c r="L93" s="5" t="n"/>
       <c r="M93" s="5" t="n"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>せきがはらのたたかい</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -14775,6 +15060,11 @@
       </c>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="5" t="n"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>ばくりょう</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -14832,6 +15122,11 @@
       </c>
       <c r="L96" s="3" t="n"/>
       <c r="M96" s="3" t="n"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>はん</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -14889,6 +15184,11 @@
       </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="5" t="n"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>ばくはんたいせい</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -14946,6 +15246,11 @@
       </c>
       <c r="L98" s="3" t="n"/>
       <c r="M98" s="3" t="n"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>ぶけしょはっと</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -15003,6 +15308,11 @@
       </c>
       <c r="L99" s="5" t="n"/>
       <c r="M99" s="5" t="n"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>えど</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -15060,6 +15370,11 @@
       </c>
       <c r="L100" s="3" t="n"/>
       <c r="M100" s="3" t="n"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>さんきんこうたい</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -15117,6 +15432,11 @@
       </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="5" t="n"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>しゅいんじょう</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -15174,6 +15494,11 @@
       </c>
       <c r="L102" s="3" t="n"/>
       <c r="M102" s="3" t="n"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>しゅいんせんぼうえき</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -15231,6 +15556,11 @@
       </c>
       <c r="L103" s="5" t="n"/>
       <c r="M103" s="5" t="n"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>にほんまち</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -15288,6 +15618,11 @@
       </c>
       <c r="L104" s="3" t="n"/>
       <c r="M104" s="3" t="n"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>きりすときょう</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -15345,6 +15680,11 @@
       </c>
       <c r="L105" s="5" t="n"/>
       <c r="M105" s="5" t="n"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>しまばら・あまくさいっき</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -15459,6 +15799,11 @@
       </c>
       <c r="L107" s="5" t="n"/>
       <c r="M107" s="5" t="n"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>しゅうもんあらため</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -15516,6 +15861,11 @@
       </c>
       <c r="L108" s="3" t="n"/>
       <c r="M108" s="3" t="n"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>ろうじゅう</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -15573,6 +15923,11 @@
       </c>
       <c r="L109" s="5" t="n"/>
       <c r="M109" s="5" t="n"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>きょうとしょしだい</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -15630,6 +15985,11 @@
       </c>
       <c r="L110" s="3" t="n"/>
       <c r="M110" s="3" t="n"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>ぶけしょはっと</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
@@ -15687,6 +16047,11 @@
       </c>
       <c r="L111" s="5" t="n"/>
       <c r="M111" s="5" t="n"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>しろ</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -15744,6 +16109,11 @@
       </c>
       <c r="L112" s="3" t="n"/>
       <c r="M112" s="3" t="n"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>さんきんこうたい</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
@@ -15801,6 +16171,11 @@
       </c>
       <c r="L113" s="5" t="n"/>
       <c r="M113" s="5" t="n"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>とくがわいえみつ</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -15858,6 +16233,11 @@
       </c>
       <c r="L114" s="3" t="n"/>
       <c r="M114" s="3" t="n"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>ぎん</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n">
@@ -15915,6 +16295,11 @@
       </c>
       <c r="L115" s="5" t="n"/>
       <c r="M115" s="5" t="n"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>きいと</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -16151,6 +16536,11 @@
       </c>
       <c r="L119" s="5" t="n"/>
       <c r="M119" s="5" t="n"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>しんぱん</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -16208,6 +16598,11 @@
       </c>
       <c r="L120" s="3" t="n"/>
       <c r="M120" s="3" t="n"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>とざまだいみょう</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="n">
@@ -16436,6 +16831,11 @@
       </c>
       <c r="L124" s="3" t="n"/>
       <c r="M124" s="3" t="n"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>さこく</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
@@ -16493,6 +16893,11 @@
       </c>
       <c r="L125" s="5" t="n"/>
       <c r="M125" s="5" t="n"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>さつま</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -16550,6 +16955,11 @@
       </c>
       <c r="L126" s="3" t="n"/>
       <c r="M126" s="3" t="n"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>きりすときょう</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="n">
@@ -16664,6 +17074,11 @@
       </c>
       <c r="L128" s="3" t="n"/>
       <c r="M128" s="3" t="n"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>でじま</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="n">
@@ -16721,6 +17136,11 @@
       </c>
       <c r="L129" s="5" t="n"/>
       <c r="M129" s="5" t="n"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>おらんだふうせつがき</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -16778,6 +17198,11 @@
       </c>
       <c r="L130" s="3" t="n"/>
       <c r="M130" s="3" t="n"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>しん</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n">
@@ -16835,6 +17260,11 @@
       </c>
       <c r="L131" s="5" t="n"/>
       <c r="M131" s="5" t="n"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>とうじんやしき</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -16892,6 +17322,11 @@
       </c>
       <c r="L132" s="3" t="n"/>
       <c r="M132" s="3" t="n"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>そうし</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="n">
@@ -16949,6 +17384,11 @@
       </c>
       <c r="L133" s="5" t="n"/>
       <c r="M133" s="5" t="n"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>ちょうせんつうしんし</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -17006,6 +17446,11 @@
       </c>
       <c r="L134" s="3" t="n"/>
       <c r="M134" s="3" t="n"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>りゅうきゅうおうこく</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="n">
@@ -17063,6 +17508,11 @@
       </c>
       <c r="L135" s="5" t="n"/>
       <c r="M135" s="5" t="n"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>けいがし</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -17120,6 +17570,11 @@
       </c>
       <c r="L136" s="3" t="n"/>
       <c r="M136" s="3" t="n"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>しゃおんし</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="n">
@@ -17177,6 +17632,11 @@
       </c>
       <c r="L137" s="5" t="n"/>
       <c r="M137" s="5" t="n"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>まつまえはん</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -17234,6 +17694,11 @@
       </c>
       <c r="L138" s="3" t="n"/>
       <c r="M138" s="3" t="n"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>あいぬみんぞく</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n">
@@ -17405,6 +17870,11 @@
       </c>
       <c r="L141" s="5" t="n"/>
       <c r="M141" s="5" t="n"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>ながさきぶぎょう</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -17637,6 +18107,11 @@
       </c>
       <c r="L145" s="5" t="n"/>
       <c r="M145" s="5" t="n"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>つしまはん</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -17694,6 +18169,11 @@
       </c>
       <c r="L146" s="3" t="n"/>
       <c r="M146" s="3" t="n"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>ちょうせんつうしんし</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n">
@@ -17808,6 +18288,11 @@
       </c>
       <c r="L148" s="3" t="n"/>
       <c r="M148" s="3" t="n"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>くろざとう</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="n">
@@ -17865,6 +18350,11 @@
       </c>
       <c r="L149" s="5" t="n"/>
       <c r="M149" s="5" t="n"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>あいぬみんぞく</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -18040,6 +18530,11 @@
       </c>
       <c r="L152" s="3" t="n"/>
       <c r="M152" s="3" t="n"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>しん</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n">
@@ -18097,6 +18592,11 @@
       </c>
       <c r="L153" s="5" t="n"/>
       <c r="M153" s="5" t="n"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>でじま</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -18325,6 +18825,11 @@
       </c>
       <c r="L157" s="5" t="n"/>
       <c r="M157" s="5" t="n"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>へいのうぶんり</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -18382,6 +18887,11 @@
       </c>
       <c r="L158" s="3" t="n"/>
       <c r="M158" s="3" t="n"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>ちょうにん</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n">
@@ -18439,6 +18949,11 @@
       </c>
       <c r="L159" s="5" t="n"/>
       <c r="M159" s="5" t="n"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>たいとう</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -18496,6 +19011,11 @@
       </c>
       <c r="L160" s="3" t="n"/>
       <c r="M160" s="3" t="n"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>ひゃくしょう</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n">
@@ -18553,6 +19073,11 @@
       </c>
       <c r="L161" s="5" t="n"/>
       <c r="M161" s="5" t="n"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>ほんびゃくしょう</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -18610,6 +19135,11 @@
       </c>
       <c r="L162" s="3" t="n"/>
       <c r="M162" s="3" t="n"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>みずのみびゃくしょう</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n">
@@ -18667,6 +19197,11 @@
       </c>
       <c r="L163" s="5" t="n"/>
       <c r="M163" s="5" t="n"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>ごにんぐみ</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -18724,6 +19259,11 @@
       </c>
       <c r="L164" s="3" t="n"/>
       <c r="M164" s="3" t="n"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>とくがわつなよし</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n">
@@ -18781,6 +19321,11 @@
       </c>
       <c r="L165" s="5" t="n"/>
       <c r="M165" s="5" t="n"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>しゅしがく</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -18838,6 +19383,11 @@
       </c>
       <c r="L166" s="3" t="n"/>
       <c r="M166" s="3" t="n"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>しんでんかいはつ</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n">
@@ -18895,6 +19445,11 @@
       </c>
       <c r="L167" s="5" t="n"/>
       <c r="M167" s="5" t="n"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>びっちゅうぐわ</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -18952,6 +19507,11 @@
       </c>
       <c r="L168" s="3" t="n"/>
       <c r="M168" s="3" t="n"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>せんばこき</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n">
@@ -19009,6 +19569,11 @@
       </c>
       <c r="L169" s="5" t="n"/>
       <c r="M169" s="5" t="n"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>とくさんぶつ</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -19066,6 +19631,11 @@
       </c>
       <c r="L170" s="3" t="n"/>
       <c r="M170" s="3" t="n"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>めんか</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n">
@@ -19123,6 +19693,11 @@
       </c>
       <c r="L171" s="5" t="n"/>
       <c r="M171" s="5" t="n"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>ほしか</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -19180,6 +19755,11 @@
       </c>
       <c r="L172" s="3" t="n"/>
       <c r="M172" s="3" t="n"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>さど</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n">
@@ -19237,6 +19817,11 @@
       </c>
       <c r="L173" s="5" t="n"/>
       <c r="M173" s="5" t="n"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>ひゃくしょう</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -19294,6 +19879,11 @@
       </c>
       <c r="L174" s="3" t="n"/>
       <c r="M174" s="3" t="n"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>ぶし</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n">
@@ -19351,6 +19941,11 @@
       </c>
       <c r="L175" s="5" t="n"/>
       <c r="M175" s="5" t="n"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>ほんびゃくしょう</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -19408,6 +20003,11 @@
       </c>
       <c r="L176" s="3" t="n"/>
       <c r="M176" s="3" t="n"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>みずのみびゃくしょう</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n">
@@ -19583,6 +20183,11 @@
       </c>
       <c r="L179" s="5" t="n"/>
       <c r="M179" s="5" t="n"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>しょうにん</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -19640,6 +20245,11 @@
       </c>
       <c r="L180" s="3" t="n"/>
       <c r="M180" s="3" t="n"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>ぶんちせいじ</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n">
@@ -19868,6 +20478,11 @@
       </c>
       <c r="L184" s="3" t="n"/>
       <c r="M184" s="3" t="n"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>あしおどうざん</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n">
@@ -19925,6 +20540,11 @@
       </c>
       <c r="L185" s="5" t="n"/>
       <c r="M185" s="5" t="n"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>いくのぎんざん</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -19982,6 +20602,11 @@
       </c>
       <c r="L186" s="3" t="n"/>
       <c r="M186" s="3" t="n"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>ぞうか</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n">
@@ -20210,6 +20835,11 @@
       </c>
       <c r="L190" s="3" t="n"/>
       <c r="M190" s="3" t="n"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>ごかいどう</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n">
@@ -20267,6 +20897,11 @@
       </c>
       <c r="L191" s="5" t="n"/>
       <c r="M191" s="5" t="n"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>ひきゃく</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -20324,6 +20959,11 @@
       </c>
       <c r="L192" s="3" t="n"/>
       <c r="M192" s="3" t="n"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>にしまわりこうろ</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="n">
@@ -20381,6 +21021,11 @@
       </c>
       <c r="L193" s="5" t="n"/>
       <c r="M193" s="5" t="n"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>ひがしまわりこうろ</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -20438,6 +21083,11 @@
       </c>
       <c r="L194" s="3" t="n"/>
       <c r="M194" s="3" t="n"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>さんと</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n">
@@ -20495,6 +21145,11 @@
       </c>
       <c r="L195" s="5" t="n"/>
       <c r="M195" s="5" t="n"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>えど</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -20552,6 +21207,11 @@
       </c>
       <c r="L196" s="3" t="n"/>
       <c r="M196" s="3" t="n"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>きょうと</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="n">
@@ -20609,6 +21269,11 @@
       </c>
       <c r="L197" s="5" t="n"/>
       <c r="M197" s="5" t="n"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>てんかのだいどころ</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -20666,6 +21331,11 @@
       </c>
       <c r="L198" s="3" t="n"/>
       <c r="M198" s="3" t="n"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>くらやしき</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n">
@@ -20723,6 +21393,11 @@
       </c>
       <c r="L199" s="5" t="n"/>
       <c r="M199" s="5" t="n"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>かぶなかま</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -20780,6 +21455,11 @@
       </c>
       <c r="L200" s="3" t="n"/>
       <c r="M200" s="3" t="n"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>げんろくぶんか</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="n">
@@ -20837,6 +21517,11 @@
       </c>
       <c r="L201" s="5" t="n"/>
       <c r="M201" s="5" t="n"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>いはらさいかく</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -20894,6 +21579,11 @@
       </c>
       <c r="L202" s="3" t="n"/>
       <c r="M202" s="3" t="n"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>ちかまつもんざえもん</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n">
@@ -20951,6 +21641,11 @@
       </c>
       <c r="L203" s="5" t="n"/>
       <c r="M203" s="5" t="n"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>はいかい</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
@@ -21008,6 +21703,11 @@
       </c>
       <c r="L204" s="3" t="n"/>
       <c r="M204" s="3" t="n"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>うきよえ</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="n">
@@ -21065,6 +21765,11 @@
       </c>
       <c r="L205" s="5" t="n"/>
       <c r="M205" s="5" t="n"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>ねんちゅうぎょうじ</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
@@ -21350,6 +22055,11 @@
       </c>
       <c r="L210" s="3" t="n"/>
       <c r="M210" s="3" t="n"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>にんぎょうじょうるり</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="n">
@@ -21464,6 +22174,11 @@
       </c>
       <c r="L212" s="3" t="n"/>
       <c r="M212" s="3" t="n"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>ひしかわもろのぶ</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="n">
@@ -21521,6 +22236,11 @@
       </c>
       <c r="L213" s="5" t="n"/>
       <c r="M213" s="5" t="n"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>おがたこうりん</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
@@ -21578,6 +22298,11 @@
       </c>
       <c r="L214" s="3" t="n"/>
       <c r="M214" s="3" t="n"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>まつおばしょう</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="n">
@@ -21635,6 +22360,11 @@
       </c>
       <c r="L215" s="5" t="n"/>
       <c r="M215" s="5" t="n"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>うきよぞうし</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
@@ -21753,6 +22483,11 @@
       </c>
       <c r="L217" s="5" t="n"/>
       <c r="M217" s="5" t="n"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>おおさか</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -21810,6 +22545,11 @@
       </c>
       <c r="L218" s="3" t="n"/>
       <c r="M218" s="3" t="n"/>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>くらやしき</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="n">
@@ -22042,6 +22782,11 @@
       </c>
       <c r="L222" s="3" t="n"/>
       <c r="M222" s="3" t="n"/>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>とくがわよしむね</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="4" t="n">
@@ -22099,6 +22844,11 @@
       </c>
       <c r="L223" s="5" t="n"/>
       <c r="M223" s="5" t="n"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>あげまいのせい</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
@@ -22156,6 +22906,11 @@
       </c>
       <c r="L224" s="3" t="n"/>
       <c r="M224" s="3" t="n"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>きょうほうのかいかく</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="4" t="n">
@@ -22213,6 +22968,11 @@
       </c>
       <c r="L225" s="5" t="n"/>
       <c r="M225" s="5" t="n"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>くじかたおさだめがき</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
@@ -22270,6 +23030,11 @@
       </c>
       <c r="L226" s="3" t="n"/>
       <c r="M226" s="3" t="n"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>しょうひんさくもつ</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="4" t="n">
@@ -22327,6 +23092,11 @@
       </c>
       <c r="L227" s="5" t="n"/>
       <c r="M227" s="5" t="n"/>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>とんやせいかないこうぎょう</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
@@ -22384,6 +23154,11 @@
       </c>
       <c r="L228" s="3" t="n"/>
       <c r="M228" s="3" t="n"/>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>ひゃくしょういっき</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="4" t="n">
@@ -22441,6 +23216,11 @@
       </c>
       <c r="L229" s="5" t="n"/>
       <c r="M229" s="5" t="n"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>うちこわし</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
@@ -22498,6 +23278,11 @@
       </c>
       <c r="L230" s="3" t="n"/>
       <c r="M230" s="3" t="n"/>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>たぬまおきつぐ</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="4" t="n">
@@ -22555,6 +23340,11 @@
       </c>
       <c r="L231" s="5" t="n"/>
       <c r="M231" s="5" t="n"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>かぶなかま</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
@@ -22612,6 +23402,11 @@
       </c>
       <c r="L232" s="3" t="n"/>
       <c r="M232" s="3" t="n"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>ながさき</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="4" t="n">
@@ -22669,6 +23464,11 @@
       </c>
       <c r="L233" s="5" t="n"/>
       <c r="M233" s="5" t="n"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>かんせいのかいかく</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
@@ -22726,6 +23526,11 @@
       </c>
       <c r="L234" s="3" t="n"/>
       <c r="M234" s="3" t="n"/>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>かせいぶんか</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="4" t="n">
@@ -22783,6 +23588,11 @@
       </c>
       <c r="L235" s="5" t="n"/>
       <c r="M235" s="5" t="n"/>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>かつしかほくさい</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
@@ -22840,6 +23650,11 @@
       </c>
       <c r="L236" s="3" t="n"/>
       <c r="M236" s="3" t="n"/>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>こくがく</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="4" t="n">
@@ -22897,6 +23712,11 @@
       </c>
       <c r="L237" s="5" t="n"/>
       <c r="M237" s="5" t="n"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>らんがく</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
@@ -22954,6 +23774,11 @@
       </c>
       <c r="L238" s="3" t="n"/>
       <c r="M238" s="3" t="n"/>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>とくがわよしむね</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="4" t="n">
@@ -23011,6 +23836,11 @@
       </c>
       <c r="L239" s="5" t="n"/>
       <c r="M239" s="5" t="n"/>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>まつだいらさだのぶ</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
@@ -23239,6 +24069,11 @@
       </c>
       <c r="L243" s="5" t="n"/>
       <c r="M243" s="5" t="n"/>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>しゅしがく</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
@@ -23418,6 +24253,11 @@
       </c>
       <c r="L246" s="3" t="n"/>
       <c r="M246" s="3" t="n"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>てらこや</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="4" t="n">
@@ -23475,6 +24315,11 @@
       </c>
       <c r="L247" s="5" t="n"/>
       <c r="M247" s="5" t="n"/>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>いのうただたか</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
@@ -23532,6 +24377,11 @@
       </c>
       <c r="L248" s="3" t="n"/>
       <c r="M248" s="3" t="n"/>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>うたがわひろしげ</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="4" t="n">
@@ -23589,6 +24439,11 @@
       </c>
       <c r="L249" s="5" t="n"/>
       <c r="M249" s="5" t="n"/>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>すぎたげんぱく</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
@@ -23821,6 +24676,11 @@
       </c>
       <c r="L253" s="5" t="n"/>
       <c r="M253" s="5" t="n"/>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>えどばくふ</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="n">
@@ -23878,6 +24738,11 @@
       </c>
       <c r="L254" s="3" t="n"/>
       <c r="M254" s="3" t="n"/>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>とよとみし</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="4" t="n">
@@ -23935,6 +24800,11 @@
       </c>
       <c r="L255" s="5" t="n"/>
       <c r="M255" s="5" t="n"/>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>ぶけしょはっと</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
@@ -23992,6 +24862,11 @@
       </c>
       <c r="L256" s="3" t="n"/>
       <c r="M256" s="3" t="n"/>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>さんきんこうたい</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n">
@@ -24049,6 +24924,11 @@
       </c>
       <c r="L257" s="5" t="n"/>
       <c r="M257" s="5" t="n"/>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>とくがわつなよし</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
@@ -24106,6 +24986,11 @@
       </c>
       <c r="L258" s="3" t="n"/>
       <c r="M258" s="3" t="n"/>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>きょうほうのかいかく</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n">
@@ -24163,6 +25048,11 @@
       </c>
       <c r="L259" s="5" t="n"/>
       <c r="M259" s="5" t="n"/>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>たぬまおきつぐ</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
@@ -24220,6 +25110,11 @@
       </c>
       <c r="L260" s="3" t="n"/>
       <c r="M260" s="3" t="n"/>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>かんせいのかいかく</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="4" t="n">
@@ -24277,6 +25172,11 @@
       </c>
       <c r="L261" s="5" t="n"/>
       <c r="M261" s="5" t="n"/>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>とくがわよしむね</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
@@ -24334,6 +25234,11 @@
       </c>
       <c r="L262" s="3" t="n"/>
       <c r="M262" s="3" t="n"/>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>ひゃくしょういっき</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="4" t="n">
@@ -24391,6 +25296,11 @@
       </c>
       <c r="L263" s="5" t="n"/>
       <c r="M263" s="5" t="n"/>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>うちこわし</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="n">
@@ -24448,6 +25358,11 @@
       </c>
       <c r="L264" s="3" t="n"/>
       <c r="M264" s="3" t="n"/>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>しんでんかいはつ</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="4" t="n">
@@ -24509,6 +25424,11 @@
         </is>
       </c>
       <c r="M265" s="5" t="n"/>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>ろうじゅう</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="n">
@@ -24570,6 +25490,11 @@
         </is>
       </c>
       <c r="M266" s="3" t="n"/>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>だいみょう</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="4" t="n">
@@ -24692,6 +25617,11 @@
         </is>
       </c>
       <c r="M268" s="3" t="n"/>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>うきよえ</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="4" t="n">
@@ -24753,6 +25683,11 @@
         </is>
       </c>
       <c r="M269" s="5" t="n"/>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>げんろくぶんか</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="n">
@@ -24814,6 +25749,11 @@
         </is>
       </c>
       <c r="M270" s="3" t="n"/>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>ぞうか</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="4" t="n">
@@ -24875,6 +25815,11 @@
         </is>
       </c>
       <c r="M271" s="5" t="n"/>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>かつしかほくさい</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
@@ -24936,6 +25881,11 @@
         </is>
       </c>
       <c r="M272" s="3" t="n"/>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>かせいぶんか</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="4" t="n">
@@ -24993,6 +25943,11 @@
       </c>
       <c r="L273" s="5" t="n"/>
       <c r="M273" s="5" t="n"/>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>しまばら・あまくさいっき</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -25168,6 +26123,11 @@
       </c>
       <c r="L276" s="3" t="n"/>
       <c r="M276" s="3" t="n"/>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>まつおばしょう</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="4" t="n">
@@ -25229,6 +26189,11 @@
         </is>
       </c>
       <c r="M277" s="5" t="n"/>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>かつしかほくさい／うたがわひろしげ</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -25465,6 +26430,11 @@
       </c>
       <c r="L281" s="5" t="n"/>
       <c r="M281" s="5" t="n"/>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>ぶけしょはっと</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
@@ -25522,6 +26492,11 @@
       </c>
       <c r="L282" s="3" t="n"/>
       <c r="M282" s="3" t="n"/>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>えど</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="4" t="n">
@@ -25579,6 +26554,11 @@
       </c>
       <c r="L283" s="5" t="n"/>
       <c r="M283" s="5" t="n"/>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>しょうぐん</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
@@ -25636,6 +26616,11 @@
       </c>
       <c r="L284" s="3" t="n"/>
       <c r="M284" s="3" t="n"/>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>まつまえ</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="4" t="n">
@@ -25811,6 +26796,11 @@
       </c>
       <c r="L287" s="5" t="n"/>
       <c r="M287" s="5" t="n"/>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>とくがわよしむね</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
@@ -25868,6 +26858,11 @@
       </c>
       <c r="L288" s="3" t="n"/>
       <c r="M288" s="3" t="n"/>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>めやすばこ</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="4" t="n">
@@ -26381,6 +27376,11 @@
       </c>
       <c r="L297" s="5" t="n"/>
       <c r="M297" s="5" t="n"/>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>きりすときょう</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
@@ -26438,6 +27438,11 @@
       </c>
       <c r="L298" s="3" t="n"/>
       <c r="M298" s="3" t="n"/>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>こうしんりょう</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="4" t="n">
@@ -26495,6 +27500,11 @@
       </c>
       <c r="L299" s="5" t="n"/>
       <c r="M299" s="5" t="n"/>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>とりひき</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
@@ -26552,6 +27562,11 @@
       </c>
       <c r="L300" s="3" t="n"/>
       <c r="M300" s="3" t="n"/>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>きりすときょう</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="4" t="n">
@@ -26609,6 +27624,11 @@
       </c>
       <c r="L301" s="5" t="n"/>
       <c r="M301" s="5" t="n"/>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>ふきょうしない</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">

--- a/data/social_data.xlsx
+++ b/data/social_data.xlsx
@@ -15003,6 +15003,11 @@
       </c>
       <c r="L94" s="3" t="n"/>
       <c r="M94" s="3" t="n"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>（えど）ばくふ</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
